--- a/data/suivi_clients_prospects.xlsx
+++ b/data/suivi_clients_prospects.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,16 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +628,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>À relancer pour commande annuelle t-shirts</t>
+          <t>Gros volume potentiel (dotation annuelle)</t>
         </is>
       </c>
     </row>
@@ -983,7 +992,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Payement souvent en retard</t>
+          <t>À relancer pour commande annuelle t-shirts</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1520,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Payement souvent en retard</t>
+          <t>À relancer pour commande annuelle t-shirts</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1580,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Prospect chaud — à rappeler</t>
+          <t>À relancer pour commande annuelle t-shirts</t>
         </is>
       </c>
     </row>
